--- a/app/content/qinhuai.xlsx
+++ b/app/content/qinhuai.xlsx
@@ -1388,7 +1388,7 @@
         <v>惊堂拍案</v>
       </c>
       <c r="C2" t="str">
-        <v>威</v>
+        <v>势</v>
       </c>
       <c r="D2" t="str">
         <v>一拍惊堂木，教他掂量抗命的分量。</v>
@@ -1399,8 +1399,8 @@
       <c r="F2">
         <v>4</v>
       </c>
-      <c r="G2">
-        <v>3</v>
+      <c r="G2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1411,7 +1411,7 @@
         <v>攻心设饵</v>
       </c>
       <c r="C3" t="str">
-        <v>利</v>
+        <v>隐</v>
       </c>
       <c r="D3" t="str">
         <v>点破「不敢直言」四字背后的怕，给他指一条生路。</v>
@@ -1434,7 +1434,7 @@
         <v>算利害账</v>
       </c>
       <c r="C4" t="str">
-        <v>利</v>
+        <v>器</v>
       </c>
       <c r="D4" t="str">
         <v>替他算清：主谋顶罪，从犯减等。</v>
@@ -1445,8 +1445,8 @@
       <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4">
-        <v>1</v>
+      <c r="G4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1457,7 +1457,7 @@
         <v>动之以情</v>
       </c>
       <c r="C5" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D5" t="str">
         <v>提他老父，提联状的乡邻，提荒沟里的夜。</v>
@@ -1480,7 +1480,7 @@
         <v>闺阁叙话</v>
       </c>
       <c r="C6" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D6" t="str">
         <v>不问案情，只问当夜席间的酒与灯。</v>
@@ -1491,8 +1491,8 @@
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6">
-        <v>1</v>
+      <c r="G6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1503,7 +1503,7 @@
         <v>条分缕析</v>
       </c>
       <c r="C7" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D7" t="str">
         <v>把时辰、人影、水痕摆成一条线，讲给她听。</v>
@@ -1526,7 +1526,7 @@
         <v>正色诘问</v>
       </c>
       <c r="C8" t="str">
-        <v>威</v>
+        <v>势</v>
       </c>
       <c r="D8" t="str">
         <v>官袍在身，一字一句问到底。</v>
@@ -1549,7 +1549,7 @@
         <v>晓以法理</v>
       </c>
       <c r="C9" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D9" t="str">
         <v>讲清知情不举与从谋的界线。</v>
@@ -1560,8 +1560,8 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
-        <v>3</v>
+      <c r="G9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1571,6 +1571,9 @@
       <c r="B10" t="str">
         <v>淡异香囊</v>
       </c>
+      <c r="C10" t="str">
+        <v>器</v>
+      </c>
       <c r="D10" t="str">
         <v>对局中出示：舱角那缕非兰非麝的异香——行家一嗅便知有诈。</v>
       </c>
@@ -1591,6 +1594,9 @@
       <c r="B11" t="str">
         <v>双层水痕拓片</v>
       </c>
+      <c r="C11" t="str">
+        <v>器</v>
+      </c>
       <c r="D11" t="str">
         <v>对局中使用：船底两次靠岸的拓片拍在案上，下一言掷地有声。（成术+3）</v>
       </c>
@@ -1611,6 +1617,9 @@
       <c r="B12" t="str">
         <v>楼庸账簿残页</v>
       </c>
+      <c r="C12" t="str">
+        <v>器</v>
+      </c>
       <c r="D12" t="str">
         <v>对局中掷出：撕去半页的大额现银账——掷出即破一切抵赖。</v>
       </c>
@@ -1631,6 +1640,9 @@
       <c r="B13" t="str">
         <v>谷公公香囊</v>
       </c>
+      <c r="C13" t="str">
+        <v>器</v>
+      </c>
       <c r="D13" t="str">
         <v>对局中使用：随身物件清册上「不见下落」的那枚香囊——线索纷至，再抽两张。</v>
       </c>
@@ -1651,6 +1663,9 @@
       <c r="B14" t="str">
         <v>素银簪</v>
       </c>
+      <c r="C14" t="str">
+        <v>器</v>
+      </c>
       <c r="D14" t="str">
         <v>对局中使用：老卒家传的簪子换了汤药钱——你却把它赎了回来。（+3）</v>
       </c>
@@ -1671,8 +1686,11 @@
       <c r="B15" t="str">
         <v>画舫苏十娘</v>
       </c>
+      <c r="C15" t="str">
+        <v>势</v>
+      </c>
       <c r="D15" t="str">
-        <v>携带：情牌 +1。秦淮的水有多深，她的账就有多细。</v>
+        <v>携带：策牌 +1。秦淮的水有多深，她的账就有多细。</v>
       </c>
       <c r="E15" t="str">
         <v>「大人问案问到奴家的船上，是奴家的体面。」</v>
@@ -1691,6 +1709,9 @@
       <c r="B16" t="str">
         <v>艄公刘舟</v>
       </c>
+      <c r="C16" t="str">
+        <v>势</v>
+      </c>
       <c r="D16" t="str">
         <v>携带：气力上限 +2。载过渡口最沉默的那位客人。</v>
       </c>
@@ -1711,8 +1732,11 @@
       <c r="B17" t="str">
         <v>监察裴清臣</v>
       </c>
+      <c r="C17" t="str">
+        <v>势</v>
+      </c>
       <c r="D17" t="str">
-        <v>携带：理牌 +1。拒签核销的硬骨头监察官。</v>
+        <v>携带：势牌 +1。拒签核销的硬骨头监察官。</v>
       </c>
       <c r="E17" t="str">
         <v>他守住了公文，没守住自家院墙。</v>
@@ -1731,8 +1755,11 @@
       <c r="B18" t="str">
         <v>游民周莽</v>
       </c>
+      <c r="C18" t="str">
+        <v>势</v>
+      </c>
       <c r="D18" t="str">
-        <v>携带：威牌 +1。荒沟里捡回半条命的汉子。</v>
+        <v>携带：隐牌 +1。荒沟里捡回半条命的汉子。</v>
       </c>
       <c r="E18" t="str">
         <v>「邀我之人身居高位」——他怕的东西，在牢外。</v>
@@ -1751,6 +1778,9 @@
       <c r="B19" t="str">
         <v>缠袋碎银</v>
       </c>
+      <c r="C19" t="str">
+        <v>器</v>
+      </c>
       <c r="D19" t="str">
         <v>资源卡：翻到即入钱袋。</v>
       </c>
@@ -1770,6 +1800,9 @@
       </c>
       <c r="B20" t="str">
         <v>漕银三十两</v>
+      </c>
+      <c r="C20" t="str">
+        <v>器</v>
       </c>
       <c r="D20" t="str">
         <v>资源卡：翻到即入钱袋。</v>
@@ -2046,7 +2079,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>威,威,利,情,威,利,理</v>
+        <v>势,隐,策,策,势,策,策</v>
       </c>
       <c r="I2" t="str">
         <v>h_wei_zhang,h_li_yin,h_li_zhang,h_qing_mu,h_li_lun</v>
@@ -2081,7 +2114,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>情,利,情,理,威,理,利</v>
+        <v>策,策,策,隐,势,策,策</v>
       </c>
       <c r="I3" t="str">
         <v>h_qing_nv,h_li_tui,h_wei_chen,h_li_zhang,h_li_lun</v>
